--- a/data/trans_dic/P22$mutuaSPriv-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,57</t>
+          <t>0,63; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,67</t>
+          <t>0,51; 2,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,15; 1,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,58</t>
+          <t>0,52; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,37</t>
+          <t>1,19; 3,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,26</t>
+          <t>0,13; 1,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,89</t>
+          <t>0,26; 1,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,84</t>
+          <t>0,63; 1,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,67</t>
+          <t>1,16; 2,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,64</t>
+          <t>0,46; 1,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,34; 1,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,9</t>
+          <t>0,74; 2,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,91</t>
+          <t>0,97; 2,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,25</t>
+          <t>1,83; 4,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,63</t>
+          <t>1,54; 3,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,52</t>
+          <t>1,0; 3,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,91</t>
+          <t>1,17; 3,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,4</t>
+          <t>1,32; 3,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,97</t>
+          <t>0,64; 2,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,17</t>
+          <t>1,44; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,59</t>
+          <t>1,27; 2,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,42</t>
+          <t>1,81; 3,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,47</t>
+          <t>1,28; 2,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,03</t>
+          <t>1,43; 3,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,1</t>
+          <t>2,07; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,28</t>
+          <t>1,59; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,03</t>
+          <t>0,54; 2,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,92</t>
+          <t>1,47; 4,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,17</t>
+          <t>1,65; 4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,62</t>
+          <t>1,77; 4,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,55</t>
+          <t>0,69; 2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,4</t>
+          <t>1,27; 4,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,14</t>
+          <t>2,22; 4,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,0</t>
+          <t>1,96; 3,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,02</t>
+          <t>0,76; 1,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,83</t>
+          <t>1,8; 4,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,19</t>
+          <t>1,45; 3,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,03</t>
+          <t>1,09; 2,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,89</t>
+          <t>2,5; 5,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,76</t>
+          <t>3,21; 5,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,7</t>
+          <t>1,08; 2,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,69</t>
+          <t>1,03; 2,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,11</t>
+          <t>1,96; 4,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,33</t>
+          <t>2,11; 4,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,62</t>
+          <t>1,38; 2,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,46</t>
+          <t>1,25; 2,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,17</t>
+          <t>2,45; 4,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,62</t>
+          <t>2,84; 4,55</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,7</t>
+          <t>1,67; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,8</t>
+          <t>1,68; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,71</t>
+          <t>1,58; 2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,4</t>
+          <t>1,99; 3,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,61</t>
+          <t>1,59; 2,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,46</t>
+          <t>1,43; 2,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,2</t>
+          <t>1,29; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,97</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,49</t>
+          <t>1,74; 2,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,47</t>
+          <t>1,69; 2,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,25</t>
+          <t>1,55; 2,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,98</t>
+          <t>2,12; 3,02</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Privado)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (seguro privado) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4879; 17761</t>
+          <t>4377; 18303</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3695; 18817</t>
+          <t>3610; 19114</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>959; 9271</t>
+          <t>984; 8670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3868; 16420</t>
+          <t>3331; 16627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8415; 23164</t>
+          <t>8205; 23189</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>935; 8799</t>
+          <t>938; 9625</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1907; 12690</t>
+          <t>1782; 12234</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4401; 12464</t>
+          <t>4268; 13105</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16195; 36763</t>
+          <t>15974; 36007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6485; 22959</t>
+          <t>6462; 23158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4537; 18552</t>
+          <t>4611; 18145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9593; 24910</t>
+          <t>9638; 26533</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9777; 27940</t>
+          <t>9322; 26692</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19047; 43266</t>
+          <t>18608; 42982</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15108; 37045</t>
+          <t>15721; 38601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11184; 41943</t>
+          <t>11969; 41845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10365; 28141</t>
+          <t>11323; 29285</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14682; 35071</t>
+          <t>13618; 34609</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6753; 20493</t>
+          <t>6624; 20879</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13996; 30398</t>
+          <t>13784; 29242</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25237; 49918</t>
+          <t>24556; 50063</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37674; 70147</t>
+          <t>37146; 69921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25180; 51021</t>
+          <t>26298; 53632</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30529; 65244</t>
+          <t>30826; 66602</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12760; 34574</t>
+          <t>14025; 34798</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11772; 32443</t>
+          <t>12056; 34052</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4182; 15402</t>
+          <t>4108; 16464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10542; 34661</t>
+          <t>10356; 32964</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10254; 28522</t>
+          <t>11309; 29526</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13233; 35942</t>
+          <t>13757; 36286</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5723; 19938</t>
+          <t>5404; 19761</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13325; 41103</t>
+          <t>11857; 41011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29517; 56390</t>
+          <t>30210; 55651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30390; 61367</t>
+          <t>30021; 60974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12085; 31050</t>
+          <t>11743; 30239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27286; 62708</t>
+          <t>29483; 66069</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12578; 29960</t>
+          <t>13642; 31266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11041; 28720</t>
+          <t>10332; 28100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23037; 45830</t>
+          <t>23389; 47455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29881; 53420</t>
+          <t>29768; 52548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11619; 27992</t>
+          <t>11199; 28404</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9643; 28246</t>
+          <t>10799; 30403</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19540; 42910</t>
+          <t>20471; 43180</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24173; 47281</t>
+          <t>23054; 46587</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28342; 51760</t>
+          <t>27221; 51373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25369; 49227</t>
+          <t>24950; 51329</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49939; 82674</t>
+          <t>48605; 82828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59424; 93375</t>
+          <t>57346; 91883</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54170; 88277</t>
+          <t>54737; 89218</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58359; 95847</t>
+          <t>57480; 96884</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55232; 91957</t>
+          <t>53673; 88165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71187; 117591</t>
+          <t>68990; 117270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>54954; 88275</t>
+          <t>53667; 87804</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51711; 87500</t>
+          <t>50914; 89206</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46180; 77953</t>
+          <t>45600; 76957</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68222; 108676</t>
+          <t>69581; 108980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>117526; 165710</t>
+          <t>115980; 162688</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117704; 172459</t>
+          <t>118191; 168854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106568; 155579</t>
+          <t>107698; 153993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>152145; 211974</t>
+          <t>150819; 215218</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutuaSPriv-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutuaSPriv-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,65</t>
+          <t>0,71; 2,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,72</t>
+          <t>0,42; 2,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,29</t>
+          <t>0,15; 1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,62</t>
+          <t>0,59; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,37</t>
+          <t>1,21; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,38</t>
+          <t>0,14; 1,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,82</t>
+          <t>0,32; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,94</t>
+          <t>0,54; 1,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,61</t>
+          <t>1,12; 2,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,65</t>
+          <t>0,47; 1,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,35</t>
+          <t>0,34; 1,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,02</t>
+          <t>0,69; 1,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,78</t>
+          <t>1,06; 2,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,23</t>
+          <t>1,8; 4,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,78</t>
+          <t>1,46; 3,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,51</t>
+          <t>2,06; 5,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,02</t>
+          <t>1,15; 3,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,35</t>
+          <t>1,44; 3,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,01</t>
+          <t>0,66; 1,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,05</t>
+          <t>1,36; 2,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,6</t>
+          <t>1,31; 2,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,41</t>
+          <t>1,83; 3,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,6</t>
+          <t>1,27; 2,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,1</t>
+          <t>1,89; 3,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,14</t>
+          <t>2,08; 5,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,49</t>
+          <t>1,57; 4,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,17</t>
+          <t>0,46; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,68</t>
+          <t>1,38; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,32</t>
+          <t>1,57; 4,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,67</t>
+          <t>1,66; 4,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,53</t>
+          <t>0,78; 2,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,39</t>
+          <t>2,54; 5,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,09</t>
+          <t>2,23; 4,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,97</t>
+          <t>1,92; 3,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,97</t>
+          <t>0,78; 1,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,03</t>
+          <t>2,24; 4,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,33</t>
+          <t>1,39; 3,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,96</t>
+          <t>1,11; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,07</t>
+          <t>2,47; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,67</t>
+          <t>3,01; 5,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,74</t>
+          <t>1,12; 2,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,89</t>
+          <t>0,93; 2,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,14</t>
+          <t>1,99; 4,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,26</t>
+          <t>2,33; 4,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,6</t>
+          <t>1,41; 2,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,57</t>
+          <t>1,22; 2,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,18</t>
+          <t>2,47; 4,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,55</t>
+          <t>2,9; 4,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,73</t>
+          <t>1,68; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,83</t>
+          <t>1,71; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,6</t>
+          <t>1,58; 2,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,39</t>
+          <t>2,33; 3,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,6</t>
+          <t>1,69; 2,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,51</t>
+          <t>1,44; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,17</t>
+          <t>1,28; 2,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>2,13; 3,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,45</t>
+          <t>1,78; 2,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,42</t>
+          <t>1,72; 2,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,22</t>
+          <t>1,52; 2,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,02</t>
+          <t>2,35; 3,17</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16968</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4377; 18303</t>
+          <t>4914; 19867</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3610; 19114</t>
+          <t>2978; 17864</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>984; 8670</t>
+          <t>983; 9896</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3331; 16627</t>
+          <t>4060; 19264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8205; 23189</t>
+          <t>8293; 23382</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>938; 9625</t>
+          <t>945; 10638</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1782; 12234</t>
+          <t>2126; 13373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4268; 13105</t>
+          <t>3944; 12947</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15974; 36007</t>
+          <t>15441; 35757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6462; 23158</t>
+          <t>6647; 22453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4611; 18145</t>
+          <t>4525; 18024</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9638; 26533</t>
+          <t>9824; 26498</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>56033</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9322; 26692</t>
+          <t>10144; 28015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18608; 42982</t>
+          <t>18292; 43160</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15721; 38601</t>
+          <t>14952; 38050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11969; 41845</t>
+          <t>21648; 54089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11323; 29285</t>
+          <t>11139; 29805</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13618; 34609</t>
+          <t>14889; 36773</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6624; 20879</t>
+          <t>6872; 20602</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13784; 29242</t>
+          <t>14603; 31450</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24556; 50063</t>
+          <t>25192; 51072</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37146; 69921</t>
+          <t>37431; 68874</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26298; 53632</t>
+          <t>26174; 50660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30826; 66602</t>
+          <t>40128; 77947</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45107</t>
+          <t>48837</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14025; 34798</t>
+          <t>14073; 36272</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12056; 34052</t>
+          <t>11875; 33735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4108; 16464</t>
+          <t>3466; 16090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10356; 32964</t>
+          <t>11076; 33019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11309; 29526</t>
+          <t>10720; 29204</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13757; 36286</t>
+          <t>12870; 36737</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5404; 19761</t>
+          <t>6096; 20510</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11857; 41011</t>
+          <t>20651; 42136</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30210; 55651</t>
+          <t>30366; 57316</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30021; 60974</t>
+          <t>29426; 60491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11743; 30239</t>
+          <t>12060; 30367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29483; 66069</t>
+          <t>36256; 64875</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>40402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73516</t>
+          <t>75635</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13642; 31266</t>
+          <t>13033; 31548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10332; 28100</t>
+          <t>10476; 29760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23389; 47455</t>
+          <t>23089; 46392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29768; 52548</t>
+          <t>29841; 54478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11199; 28404</t>
+          <t>11573; 27418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10799; 30403</t>
+          <t>9801; 29485</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20471; 43180</t>
+          <t>20808; 43182</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23054; 46587</t>
+          <t>26073; 47479</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27221; 51373</t>
+          <t>27825; 52114</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24950; 51329</t>
+          <t>24297; 49452</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48605; 82828</t>
+          <t>48823; 80860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57346; 91883</t>
+          <t>61150; 94976</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>103212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>181220</t>
+          <t>197473</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54737; 89218</t>
+          <t>55000; 88610</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57480; 96884</t>
+          <t>58453; 97014</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53673; 88165</t>
+          <t>53681; 88495</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68990; 117270</t>
+          <t>82163; 130113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53667; 87804</t>
+          <t>57167; 90229</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50914; 89206</t>
+          <t>51335; 87605</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45600; 76957</t>
+          <t>45226; 76426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69581; 108980</t>
+          <t>79386; 113514</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>115980; 162688</t>
+          <t>118130; 166093</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118191; 168854</t>
+          <t>120082; 169987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107698; 153993</t>
+          <t>105444; 153728</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>150819; 215218</t>
+          <t>170832; 230548</t>
         </is>
       </c>
     </row>
